--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N169_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N169_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.17763448431759</v>
+        <v>8.966365603701608</v>
       </c>
       <c r="D2" t="n">
-        <v>44.04742753586934</v>
+        <v>7.157706974578768</v>
       </c>
       <c r="E2" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F2" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.6834693868261</v>
+        <v>5.311063775359241</v>
       </c>
       <c r="D3" t="n">
-        <v>24.01609435358522</v>
+        <v>3.902615332457598</v>
       </c>
       <c r="E3" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F3" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.50362299817223</v>
+        <v>5.606838737202988</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7169016048338</v>
+        <v>1.741496510785492</v>
       </c>
       <c r="E4" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F4" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.609772228646444</v>
+        <v>0.7490879871550471</v>
       </c>
       <c r="D5" t="n">
-        <v>4.909376743303503</v>
+        <v>0.7977737207868193</v>
       </c>
       <c r="E5" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F5" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.5071414000116</v>
+        <v>2.844910477501885</v>
       </c>
       <c r="D6" t="n">
-        <v>17.21971680006254</v>
+        <v>2.798203980010163</v>
       </c>
       <c r="E6" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F6" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.43068747487202</v>
+        <v>7.057486714666704</v>
       </c>
       <c r="D7" t="n">
-        <v>42.70149804262125</v>
+        <v>6.938993431925954</v>
       </c>
       <c r="E7" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F7" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.06473720544871</v>
+        <v>4.398019795885416</v>
       </c>
       <c r="D8" t="n">
-        <v>26.82932657226817</v>
+        <v>4.359765567993578</v>
       </c>
       <c r="E8" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F8" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.43608329051593</v>
+        <v>3.808363534708839</v>
       </c>
       <c r="D9" t="n">
-        <v>44.50280890011326</v>
+        <v>7.231706446268404</v>
       </c>
       <c r="E9" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F9" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.97655391063896</v>
+        <v>5.196190010478832</v>
       </c>
       <c r="D10" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="E10" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F10" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.30394050424695</v>
+        <v>3.29939033194013</v>
       </c>
       <c r="D11" t="n">
-        <v>48.10405388322278</v>
+        <v>7.816908756023701</v>
       </c>
       <c r="E11" t="n">
-        <v>13.35468356676843</v>
+        <v>2.17013607959987</v>
       </c>
       <c r="F11" t="n">
-        <v>15.5695474766085</v>
+        <v>2.530051464948881</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
